--- a/tests/testthat/golden/P09.xlsx
+++ b/tests/testthat/golden/P09.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="10" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="20" uniqueCount="6">
   <si>
     <t>One column</t>
   </si>
@@ -37,7 +37,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -68,6 +68,16 @@
     <font>
       <sz val="10"/>
       <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -79,7 +89,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -116,11 +126,32 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -170,6 +201,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -188,42 +234,42 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="13" t="s">
+      <c r="A5" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>5</v>
       </c>
     </row>
